--- a/assets/docs/lop4/Khoa hoc - Lop 4.xlsx
+++ b/assets/docs/lop4/Khoa hoc - Lop 4.xlsx
@@ -874,7 +874,7 @@
       <c r="H14" s="4" t="inlineStr">
         <is>
           <t>Năng lực số 1.2 CB2a: HS nêu được vì sao phải theo dõi bản tin mới nhất và không chia sẻ tin bão chưa kiểm chứng.
-STEM: Gió, bão (Khoa học – Công nghệ) — dạy thay cho tiết này.</t>
+STEM: Dụng cụ đo sức gió (Khoa học – Công nghệ – Toán) — dạy thay cho tiết này.</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,8 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.2 CB2a: HS nêu được vì sao phải theo dõi bản tin mới nhất và không chia sẻ tin bão chưa kiểm chứng.</t>
+          <t>Năng lực số 1.2 CB2a: HS nêu được vì sao phải theo dõi bản tin mới nhất và không chia sẻ tin bão chưa kiểm chứng.
+STEM: Dụng cụ đo sức gió (Khoa học – Công nghệ – Toán) — dạy thay cho tiết này.</t>
         </is>
       </c>
     </row>
@@ -1011,19 +1012,19 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Ôn tập, kiểm tra, đánh giá</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr"/>
       <c r="D19" s="4" t="inlineStr"/>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Ôn tập giữa học kì I</t>
+          <t>Bài 9. Vai trò của ánh sáng (Tiết 1)</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>2 tiết</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
@@ -1031,7 +1032,11 @@
           <t>16</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr"/>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số 5.1 CB2a: HS giải thích được sự tạo thành bóng và ánh sáng truyền theo đường thẳng nhờ mô phỏng và thí nghiệm.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -1041,27 +1046,27 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Ôn tập, kiểm tra, đánh giá</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr"/>
       <c r="D20" s="4" t="inlineStr"/>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra định kì giữa học kì I</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
+          <t>Bài 9. Vai trò của ánh sáng (Tiết 2)</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="4" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr"/>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số 5.1 CB2a: HS giải thích được sự tạo thành bóng và ánh sáng truyền theo đường thẳng nhờ mô phỏng và thí nghiệm.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -1078,7 +1083,7 @@
       <c r="D21" s="4" t="inlineStr"/>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Bài 9. Vai trò của ánh sáng (Tiết 1)</t>
+          <t>Bài 10. Âm thanh và sự truyền âm thanh (Tiết 1)</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -1093,7 +1098,7 @@
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 5.1 CB2a: HS giải thích được sự tạo thành bóng và ánh sáng truyền theo đường thẳng nhờ mô phỏng và thí nghiệm.</t>
+          <t>Năng lực số 5.2 CB2b: HS đo, ghi và so sánh được mức ồn ở các vị trí khác nhau bằng ứng dụng đo độ ồn.</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1117,7 @@
       <c r="D22" s="4" t="inlineStr"/>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Bài 9. Vai trò của ánh sáng (Tiết 2)</t>
+          <t>Bài 10. Âm thanh và sự truyền âm thanh (Tiết 2)</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr"/>
@@ -1123,7 +1128,7 @@
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 5.1 CB2a: HS giải thích được sự tạo thành bóng và ánh sáng truyền theo đường thẳng nhờ mô phỏng và thí nghiệm.</t>
+          <t>Năng lực số 5.2 CB2b: HS đo, ghi và so sánh được mức ồn ở các vị trí khác nhau bằng ứng dụng đo độ ồn.</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1147,7 @@
       <c r="D23" s="4" t="inlineStr"/>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Bài 10. Âm thanh và sự truyền âm thanh (Tiết 1)</t>
+          <t>Bài 11. Âm thanh trong cuộc sống (Tiết 1)</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -1157,7 +1162,9 @@
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 5.2 CB2b: HS đo, ghi và so sánh được mức ồn ở các vị trí khác nhau bằng ứng dụng đo độ ồn.</t>
+          <t>NLS-ST: Tạo sản phẩm học tập số đơn giản (sơ đồ, áp phích) trình bày kết quả.
+Năng lực số 5.2 CB2b: HS đo, ghi và so sánh được mức ồn ở các vị trí khác nhau bằng ứng dụng đo độ ồn.
+STEM: Âm thanh trong cuộc sống (Khoa học – Âm nhạc) — dạy thay cho tiết này.</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1183,7 @@
       <c r="D24" s="4" t="inlineStr"/>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Bài 10. Âm thanh và sự truyền âm thanh (Tiết 2)</t>
+          <t>Bài 11. Âm thanh trong cuộc sống (Tiết 2)</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr"/>
@@ -1206,7 +1213,7 @@
       <c r="D25" s="4" t="inlineStr"/>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Bài 11. Âm thanh trong cuộc sống (Tiết 1)</t>
+          <t>Bài 12. Nhiệt độ và sự truyền nhiệt (Tiết 1)</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -1221,9 +1228,8 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>NLS-ST: Tạo sản phẩm học tập số đơn giản (sơ đồ, áp phích) trình bày kết quả.
-Năng lực số 5.2 CB2b: HS đo, ghi và so sánh được mức ồn ở các vị trí khác nhau bằng ứng dụng đo độ ồn.
-STEM: Âm thanh trong cuộc sống (Khoa học – Âm nhạc) — dạy thay cho tiết này.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở bài “Nhiệt độ và sự truyền nhiệt”, GV chiếu ảnh phóng to mặt nhiệt kế để cả lớp cùng đọc đúng số chỉ
+Năng lực số Miền 5 (Cơ bản, bậc 2): HS ghi kết quả đo vào bảng chiếu trên màn hình rồi cùng đối chiếu; khi số liệu các nhóm khác nhau, cả lớp tìm nguyên nhân là đặt nhiệt kế gần cửa sổ</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1248,7 @@
       <c r="D26" s="4" t="inlineStr"/>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Bài 11. Âm thanh trong cuộc sống (Tiết 2)</t>
+          <t>Bài 12. Nhiệt độ và sự truyền nhiệt (Tiết 2)</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr"/>
@@ -1253,7 +1259,7 @@
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 5.2 CB2b: HS đo, ghi và so sánh được mức ồn ở các vị trí khác nhau bằng ứng dụng đo độ ồn.</t>
+          <t>Năng lực số 1.3 CB2a: HS ghi số đo nhiệt độ theo từng mốc thời gian vào bảng trên máy và tìm lại được số liệu của nhóm mình để so sánh.</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1278,7 @@
       <c r="D27" s="4" t="inlineStr"/>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Bài 12. Nhiệt độ và sự truyền nhiệt (Tiết 1)</t>
+          <t>Bài 13. Vật dẫn nhiệt tốt, vật dẫn nhiệt kém (Tiết 1)</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -1287,8 +1293,9 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở bài “Nhiệt độ và sự truyền nhiệt”, GV chiếu ảnh phóng to mặt nhiệt kế để cả lớp cùng đọc đúng số chỉ
-Năng lực số Miền 5 (Cơ bản, bậc 2): HS ghi kết quả đo vào bảng chiếu trên màn hình rồi cùng đối chiếu; khi số liệu các nhóm khác nhau, cả lớp tìm nguyên nhân là đặt nhiệt kế gần cửa sổ</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở bài vật dẫn nhiệt tốt và vật dẫn nhiệt kém, GV chiếu mô phỏng nhiệt truyền qua thìa kim loại và thìa gỗ cắm trong cốc nước nóng
+Năng lực số Miền 5 (Cơ bản, bậc 2): HS ghi kết quả thí nghiệm vào bảng chiếu trên màn hình rồi đối chiếu với dự đoán; khi kết quả các nhóm khác nhau
+STEM: Dẫn nhiệt (Khoa học – Công nghệ) — dạy thay cho tiết này.</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1314,7 @@
       <c r="D28" s="4" t="inlineStr"/>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Bài 12. Nhiệt độ và sự truyền nhiệt (Tiết 2)</t>
+          <t>Bài 13. Vật dẫn nhiệt tốt, vật dẫn nhiệt kém (Tiết 2)</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr"/>
@@ -1316,11 +1323,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.3 CB2a: HS ghi số đo nhiệt độ theo từng mốc thời gian vào bảng trên máy và tìm lại được số liệu của nhóm mình để so sánh.</t>
-        </is>
-      </c>
+      <c r="H28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -1337,12 +1340,12 @@
       <c r="D29" s="4" t="inlineStr"/>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Bài 13. Vật dẫn nhiệt tốt, vật dẫn nhiệt kém (Tiết 1)</t>
+          <t>Bài 14. Ôn tập chủ đề Năng lượng</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>2 tiết</t>
+          <t>1 tiết</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
@@ -1350,12 +1353,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở bài vật dẫn nhiệt tốt và vật dẫn nhiệt kém, GV chiếu mô phỏng nhiệt truyền qua thìa kim loại và thìa gỗ cắm trong cốc nước nóng
-Năng lực số Miền 5 (Cơ bản, bậc 2): HS ghi kết quả thí nghiệm vào bảng chiếu trên màn hình rồi đối chiếu với dự đoán; khi kết quả các nhóm khác nhau</t>
-        </is>
-      </c>
+      <c r="H29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -1365,23 +1363,31 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: Năng lượng</t>
+          <t>Chủ đề 3: Thực vật và động vật</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr"/>
       <c r="D30" s="4" t="inlineStr"/>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Bài 13. Vật dẫn nhiệt tốt, vật dẫn nhiệt kém (Tiết 2)</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr"/>
+          <t>Bài 15. Thực vật cần gì để sống? (Tiết 1)</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>3 tiết</t>
+        </is>
+      </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr"/>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số 1.3 CB2a: HS ghi, đọc được bảng theo dõi và chuỗi ảnh để rút ra kết luận từ số liệu của chính mình.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -1391,27 +1397,27 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: Năng lượng</t>
+          <t>Chủ đề 3: Thực vật và động vật</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr"/>
       <c r="D31" s="4" t="inlineStr"/>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Bài 14. Ôn tập chủ đề Năng lượng</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
+          <t>Bài 15. Thực vật cần gì để sống? (Tiết 2)</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr"/>
       <c r="G31" s="4" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr"/>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số 1.3 CB2a: HS ghi, đọc được bảng theo dõi và chuỗi ảnh để rút ra kết luận từ số liệu của chính mình.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -1428,14 +1434,10 @@
       <c r="D32" s="4" t="inlineStr"/>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Bài 15. Thực vật cần gì để sống? (Tiết 1)</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>3 tiết</t>
-        </is>
-      </c>
+          <t>Bài 15. Thực vật cần gì để sống? (Tiết 3)</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr"/>
       <c r="G32" s="4" t="inlineStr">
         <is>
           <t>29</t>
@@ -1462,10 +1464,14 @@
       <c r="D33" s="4" t="inlineStr"/>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Bài 15. Thực vật cần gì để sống? (Tiết 2)</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr"/>
+          <t>Bài 16. Động vật cần gì để sống? (Tiết 1)</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>3 tiết</t>
+        </is>
+      </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
           <t>30</t>
@@ -1492,7 +1498,7 @@
       <c r="D34" s="4" t="inlineStr"/>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Bài 15. Thực vật cần gì để sống? (Tiết 3)</t>
+          <t>Bài 16. Động vật cần gì để sống? (Tiết 2)</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr"/>
@@ -1522,14 +1528,10 @@
       <c r="D35" s="4" t="inlineStr"/>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Bài 16. Động vật cần gì để sống? (Tiết 1)</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>3 tiết</t>
-        </is>
-      </c>
+          <t>Bài 16. Động vật cần gì để sống? (Tiết 3)</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr"/>
       <c r="G35" s="4" t="inlineStr">
         <is>
           <t>32</t>
@@ -1556,10 +1558,14 @@
       <c r="D36" s="4" t="inlineStr"/>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Bài 16. Động vật cần gì để sống? (Tiết 2)</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr"/>
+          <t>Bài 17. Chăm sóc cây trồng, vật nuôi (Tiết 1)</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>2 tiết</t>
+        </is>
+      </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
           <t>33</t>
@@ -1586,7 +1592,7 @@
       <c r="D37" s="4" t="inlineStr"/>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Bài 16. Động vật cần gì để sống? (Tiết 3)</t>
+          <t>Bài 17. Chăm sóc cây trồng, vật nuôi (Tiết 2)</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr"/>
@@ -1597,7 +1603,7 @@
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.3 CB2a: HS ghi, đọc được bảng theo dõi và chuỗi ảnh để rút ra kết luận từ số liệu của chính mình.</t>
+          <t>Năng lực số 1.3 CB2a: HS ghi bảng theo dõi việc chăm sóc vật nuôi ở nhà trong một tuần (ngày, việc đã làm, biểu hiện của con vật) và đọc lại bảng để rút ra nhận xét.</t>
         </is>
       </c>
     </row>
@@ -1609,14 +1615,14 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Ôn tập, kiểm tra, đánh giá</t>
+          <t>Chủ đề 3: Thực vật và động vật</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr"/>
       <c r="D38" s="4" t="inlineStr"/>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Ôn tập cuối học kì I</t>
+          <t>Bài 18. Ôn tập chủ đề Thực vật và động vật</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -1669,14 +1675,14 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: Thực vật và động vật</t>
+          <t>Chủ đề 4: Nấm</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr"/>
       <c r="D40" s="4" t="inlineStr"/>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Bài 17. Chăm sóc cây trồng, vật nuôi (Tiết 1)</t>
+          <t>Bài 19. Đặc điểm chung của nấm (Tiết 1)</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -1691,7 +1697,7 @@
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.3 CB2a: HS ghi, đọc được bảng theo dõi và chuỗi ảnh để rút ra kết luận từ số liệu của chính mình.</t>
+          <t>Năng lực số 1.1 CB2c: HS quan sát ảnh hiển vi để mô tả đặc điểm của nấm mà mắt thường không thấy.</t>
         </is>
       </c>
     </row>
@@ -1703,14 +1709,14 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: Thực vật và động vật</t>
+          <t>Chủ đề 4: Nấm</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr"/>
       <c r="D41" s="4" t="inlineStr"/>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Bài 17. Chăm sóc cây trồng, vật nuôi (Tiết 2)</t>
+          <t>Bài 19. Đặc điểm chung của nấm (Tiết 2)</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr"/>
@@ -1721,7 +1727,7 @@
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.3 CB2a: HS ghi bảng theo dõi việc chăm sóc vật nuôi ở nhà trong một tuần (ngày, việc đã làm, biểu hiện của con vật) và đọc lại bảng để rút ra nhận xét.</t>
+          <t>Năng lực số 1.1 CB2c: HS quan sát ảnh hiển vi để mô tả đặc điểm của nấm mà mắt thường không thấy.</t>
         </is>
       </c>
     </row>
@@ -1733,19 +1739,19 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: Thực vật và động vật</t>
+          <t>Chủ đề 4: Nấm</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr"/>
       <c r="D42" s="4" t="inlineStr"/>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Bài 18. Ôn tập chủ đề Thực vật và động vật</t>
+          <t>Bài 20. Nấm ăn và nấm trong chế biến thực phẩm (Tiết 1)</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>2 tiết</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
@@ -1753,7 +1759,11 @@
           <t>39</t>
         </is>
       </c>
-      <c r="H42" s="4" t="inlineStr"/>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số 1.1 CB2c: HS quan sát ảnh hiển vi để mô tả đặc điểm của nấm mà mắt thường không thấy.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -1770,14 +1780,10 @@
       <c r="D43" s="4" t="inlineStr"/>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Bài 19. Đặc điểm chung của nấm (Tiết 1)</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>2 tiết</t>
-        </is>
-      </c>
+          <t>Bài 20. Nấm ăn và nấm trong chế biến thực phẩm (Tiết 2)</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr"/>
       <c r="G43" s="4" t="inlineStr">
         <is>
           <t>40</t>
@@ -1804,10 +1810,14 @@
       <c r="D44" s="4" t="inlineStr"/>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Bài 19. Đặc điểm chung của nấm (Tiết 2)</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr"/>
+          <t>Bài 21. Nấm gây hỏng thực phẩm và nấm độc (Tiết 1)</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>2 tiết</t>
+        </is>
+      </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
           <t>41</t>
@@ -1834,14 +1844,10 @@
       <c r="D45" s="4" t="inlineStr"/>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Bài 20. Nấm ăn và nấm trong chế biến thực phẩm (Tiết 1)</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>2 tiết</t>
-        </is>
-      </c>
+          <t>Bài 21. Nấm gây hỏng thực phẩm và nấm độc (Tiết 2)</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr"/>
       <c r="G45" s="4" t="inlineStr">
         <is>
           <t>42</t>
@@ -1868,20 +1874,20 @@
       <c r="D46" s="4" t="inlineStr"/>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>Bài 20. Nấm ăn và nấm trong chế biến thực phẩm (Tiết 2)</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr"/>
+          <t>Bài 22. Ôn tập chủ đề Nấm</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.1 CB2c: HS quan sát ảnh hiển vi để mô tả đặc điểm của nấm mà mắt thường không thấy.</t>
-        </is>
-      </c>
+      <c r="H46" s="4" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -1891,14 +1897,14 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: Nấm</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr"/>
       <c r="D47" s="4" t="inlineStr"/>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Bài 21. Nấm gây hỏng thực phẩm và nấm độc (Tiết 1)</t>
+          <t>Bài 23. Vai trò của chất dinh dưỡng đối với cơ thể (Tiết 1)</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -1913,7 +1919,8 @@
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS quan sát ảnh hiển vi để mô tả đặc điểm của nấm mà mắt thường không thấy.</t>
+          <t>Năng lực số 5.2 CB2b: HS lập được bảng thực đơn theo nhóm chất dinh dưỡng và tự nhận xét bữa ăn của mình.
+KNS: KN chăm sóc sức khoẻ bản thân và phòng tránh bệnh tật.</t>
         </is>
       </c>
     </row>
@@ -1925,14 +1932,14 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: Nấm</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr"/>
       <c r="D48" s="4" t="inlineStr"/>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Bài 21. Nấm gây hỏng thực phẩm và nấm độc (Tiết 2)</t>
+          <t>Bài 23. Vai trò của chất dinh dưỡng đối với cơ thể (Tiết 2)</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr"/>
@@ -1943,7 +1950,7 @@
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS quan sát ảnh hiển vi để mô tả đặc điểm của nấm mà mắt thường không thấy.</t>
+          <t>Năng lực số 5.2 CB2b: HS lập được bảng thực đơn theo nhóm chất dinh dưỡng và tự nhận xét bữa ăn của mình.</t>
         </is>
       </c>
     </row>
@@ -1955,19 +1962,19 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: Nấm</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr"/>
       <c r="D49" s="4" t="inlineStr"/>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Bài 22. Ôn tập chủ đề Nấm</t>
+          <t>Bài 24. Chế độ ăn uống cân bằng (Tiết 1)</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>1 tiết</t>
+          <t>3 tiết</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
@@ -1975,102 +1982,7 @@
           <t>46</t>
         </is>
       </c>
-      <c r="H49" s="4" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>Chủ đề 5: Con người và sức khoẻ</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr"/>
-      <c r="D50" s="4" t="inlineStr"/>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>Bài 23. Vai trò của chất dinh dưỡng đối với cơ thể (Tiết 1)</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>2 tiết</t>
-        </is>
-      </c>
-      <c r="G50" s="4" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB2b: HS lập được bảng thực đơn theo nhóm chất dinh dưỡng và tự nhận xét bữa ăn của mình.
-KNS: KN chăm sóc sức khoẻ bản thân và phòng tránh bệnh tật.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>Chủ đề 5: Con người và sức khoẻ</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr"/>
-      <c r="D51" s="4" t="inlineStr"/>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>Bài 23. Vai trò của chất dinh dưỡng đối với cơ thể (Tiết 2)</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr"/>
-      <c r="G51" s="4" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="H51" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB2b: HS lập được bảng thực đơn theo nhóm chất dinh dưỡng và tự nhận xét bữa ăn của mình.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>Chủ đề 5: Con người và sức khoẻ</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr"/>
-      <c r="D52" s="4" t="inlineStr"/>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>Bài 24. Chế độ ăn uống cân bằng (Tiết 1)</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>3 tiết</t>
-        </is>
-      </c>
-      <c r="G52" s="4" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="H52" s="4" t="inlineStr">
+      <c r="H49" s="4" t="inlineStr">
         <is>
           <t>NLS-ST: Tạo sản phẩm học tập số đơn giản (sơ đồ, áp phích) trình bày kết quả.
 Năng lực số 5.2 CB2b: HS lập được bảng thực đơn theo nhóm chất dinh dưỡng và tự nhận xét bữa ăn của mình.
@@ -2079,6 +1991,101 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr"/>
+      <c r="D50" s="4" t="inlineStr"/>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>Bài 24. Chế độ ăn uống cân bằng (Tiết 2)</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr"/>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số 5.2 CB2b: HS lập được bảng thực đơn theo nhóm chất dinh dưỡng và tự nhận xét bữa ăn của mình.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr"/>
+      <c r="D51" s="4" t="inlineStr"/>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>Bài 24. Chế độ ăn uống cân bằng (Tiết 3)</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr"/>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số 5.2 CB2b: HS lập được bảng thực đơn theo nhóm chất dinh dưỡng và tự nhận xét bữa ăn của mình.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr"/>
+      <c r="D52" s="4" t="inlineStr"/>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>Bài 25. Một số bệnh liên quan đến dinh dưỡng (Tiết 1)</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>3 tiết</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số 5.2 CB2b: HS lập được bảng thực đơn theo nhóm chất dinh dưỡng và tự nhận xét bữa ăn của mình.
+KNS: KN chăm sóc sức khoẻ bản thân và phòng tránh bệnh tật.</t>
+        </is>
+      </c>
+    </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
@@ -2094,7 +2101,7 @@
       <c r="D53" s="4" t="inlineStr"/>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Bài 24. Chế độ ăn uống cân bằng (Tiết 2)</t>
+          <t>Bài 25. Một số bệnh liên quan đến dinh dưỡng (Tiết 2)</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr"/>
@@ -2124,7 +2131,7 @@
       <c r="D54" s="4" t="inlineStr"/>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Bài 24. Chế độ ăn uống cân bằng (Tiết 3)</t>
+          <t>Bài 25. Một số bệnh liên quan đến dinh dưỡng (Tiết 3)</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr"/>
@@ -2154,12 +2161,12 @@
       <c r="D55" s="4" t="inlineStr"/>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Bài 25. Một số bệnh liên quan đến dinh dưỡng (Tiết 1)</t>
+          <t>Bài 26. Thực phẩm an toàn (Tiết 1)</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>3 tiết</t>
+          <t>2 tiết</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
@@ -2169,8 +2176,8 @@
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 5.2 CB2b: HS lập được bảng thực đơn theo nhóm chất dinh dưỡng và tự nhận xét bữa ăn của mình.
-KNS: KN chăm sóc sức khoẻ bản thân và phòng tránh bệnh tật.</t>
+          <t>Năng lực số 5.1 CB2a: HS nêu được cách xử lí khi gặp thực phẩm hết hạn, bao bì hỏng hoặc không rõ nguồn gốc.
+KNS: KN an toàn khi thực hành: làm đúng hướng dẫn, không tự ý thử nghiệm nguy hiểm.</t>
         </is>
       </c>
     </row>
@@ -2189,7 +2196,7 @@
       <c r="D56" s="4" t="inlineStr"/>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Bài 25. Một số bệnh liên quan đến dinh dưỡng (Tiết 2)</t>
+          <t>Bài 26. Thực phẩm an toàn (Tiết 2)</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr"/>
@@ -2200,7 +2207,7 @@
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 5.2 CB2b: HS lập được bảng thực đơn theo nhóm chất dinh dưỡng và tự nhận xét bữa ăn của mình.</t>
+          <t>Năng lực số 5.1 CB2a: HS nêu được cách xử lí khi gặp thực phẩm hết hạn, bao bì hỏng hoặc không rõ nguồn gốc.</t>
         </is>
       </c>
     </row>
@@ -2219,10 +2226,14 @@
       <c r="D57" s="4" t="inlineStr"/>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Bài 25. Một số bệnh liên quan đến dinh dưỡng (Tiết 3)</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr"/>
+          <t>Bài 27. Phòng tránh đuối nước (Tiết 1)</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>2 tiết</t>
+        </is>
+      </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
           <t>54</t>
@@ -2230,7 +2241,7 @@
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 5.2 CB2b: HS lập được bảng thực đơn theo nhóm chất dinh dưỡng và tự nhận xét bữa ăn của mình.</t>
+          <t>Năng lực số 1.1 CB2c: HS nêu và làm được các bước cứu người đuối nước an toàn từ trên bờ.</t>
         </is>
       </c>
     </row>
@@ -2242,27 +2253,27 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Ôn tập, kiểm tra, đánh giá</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr"/>
       <c r="D58" s="4" t="inlineStr"/>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra định kì giữa học kì II</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
+          <t>Bài 27. Phòng tránh đuối nước (Tiết 2)</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr"/>
       <c r="G58" s="4" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="H58" s="4" t="inlineStr"/>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số 1.1 CB2c: HS nêu và làm được các bước cứu người đuối nước an toàn từ trên bờ.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -2279,7 +2290,7 @@
       <c r="D59" s="4" t="inlineStr"/>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Bài 26. Thực phẩm an toàn (Tiết 1)</t>
+          <t>Bài 28. Ôn tập chủ đề Con người và sức khoẻ (Tiết 1)</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
@@ -2292,12 +2303,7 @@
           <t>56</t>
         </is>
       </c>
-      <c r="H59" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.1 CB2a: HS nêu được cách xử lí khi gặp thực phẩm hết hạn, bao bì hỏng hoặc không rõ nguồn gốc.
-KNS: KN an toàn khi thực hành: làm đúng hướng dẫn, không tự ý thử nghiệm nguy hiểm.</t>
-        </is>
-      </c>
+      <c r="H59" s="4" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -2314,7 +2320,7 @@
       <c r="D60" s="4" t="inlineStr"/>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Bài 26. Thực phẩm an toàn (Tiết 2)</t>
+          <t>Bài 28. Ôn tập chủ đề Con người và sức khoẻ (Tiết 2)</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr"/>
@@ -2323,11 +2329,7 @@
           <t>57</t>
         </is>
       </c>
-      <c r="H60" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.1 CB2a: HS nêu được cách xử lí khi gặp thực phẩm hết hạn, bao bì hỏng hoặc không rõ nguồn gốc.</t>
-        </is>
-      </c>
+      <c r="H60" s="4" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -2337,19 +2339,19 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: Con người và sức khoẻ</t>
+          <t>Chủ đề 6: Sinh vật và môi trường</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr"/>
       <c r="D61" s="4" t="inlineStr"/>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Bài 27. Phòng tránh đuối nước (Tiết 1)</t>
+          <t>Bài 29. Chuỗi thức ăn trong tự nhiên (Tiết 1)</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>2 tiết</t>
+          <t>3 tiết</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
@@ -2359,7 +2361,9 @@
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS nêu và làm được các bước cứu người đuối nước an toàn từ trên bờ.</t>
+          <t>Năng lực số 5.2 CB2b: HS dựng đúng chuỗi thức ăn trên học liệu tương tác và tự sửa khi máy báo sai.
+STEM: Chuỗi thức ăn trong tự nhiên (Khoa học – Mĩ thuật) — dạy thay cho tiết này.
+KNS: KN chăm sóc sức khoẻ bản thân và phòng tránh bệnh tật.</t>
         </is>
       </c>
     </row>
@@ -2371,14 +2375,14 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: Con người và sức khoẻ</t>
+          <t>Chủ đề 6: Sinh vật và môi trường</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr"/>
       <c r="D62" s="4" t="inlineStr"/>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Bài 27. Phòng tránh đuối nước (Tiết 2)</t>
+          <t>Bài 29. Chuỗi thức ăn trong tự nhiên (Tiết 2)</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr"/>
@@ -2389,7 +2393,7 @@
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS nêu và làm được các bước cứu người đuối nước an toàn từ trên bờ.</t>
+          <t>Năng lực số 2.5 CB2a: HS trình chiếu sơ đồ của nhóm và góp ý cho nhóm bạn một cách lịch sự, đúng mực.</t>
         </is>
       </c>
     </row>
@@ -2401,27 +2405,27 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: Con người và sức khoẻ</t>
+          <t>Chủ đề 6: Sinh vật và môi trường</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr"/>
       <c r="D63" s="4" t="inlineStr"/>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Bài 28. Ôn tập chủ đề Con người và sức khoẻ (Tiết 1)</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t>2 tiết</t>
-        </is>
-      </c>
+          <t>Bài 29. Chuỗi thức ăn trong tự nhiên (Tiết 3)</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr"/>
       <c r="G63" s="4" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="H63" s="4" t="inlineStr"/>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số 5.2 CB2b: HS dựng đúng chuỗi thức ăn trên học liệu tương tác và tự sửa khi máy báo sai.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -2431,23 +2435,32 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: Con người và sức khoẻ</t>
+          <t>Chủ đề 6: Sinh vật và môi trường</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr"/>
       <c r="D64" s="4" t="inlineStr"/>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>Bài 28. Ôn tập chủ đề Con người và sức khoẻ (Tiết 2)</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="inlineStr"/>
+          <t>Bài 30. Vai trò của thực vật trong chuỗi thức ăn (Tiết 1)</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>3 tiết</t>
+        </is>
+      </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
           <t>61</t>
         </is>
       </c>
-      <c r="H64" s="4" t="inlineStr"/>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số 5.2 CB2b: HS dựng đúng chuỗi thức ăn trên học liệu tương tác và tự sửa khi máy báo sai.
+KNS: KN chăm sóc sức khoẻ bản thân và phòng tránh bệnh tật.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -2464,14 +2477,10 @@
       <c r="D65" s="4" t="inlineStr"/>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>Bài 29. Chuỗi thức ăn trong tự nhiên (Tiết 1)</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>3 tiết</t>
-        </is>
-      </c>
+          <t>Bài 30. Vai trò của thực vật trong chuỗi thức ăn (Tiết 2)</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr"/>
       <c r="G65" s="4" t="inlineStr">
         <is>
           <t>62</t>
@@ -2479,9 +2488,7 @@
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 5.2 CB2b: HS dựng đúng chuỗi thức ăn trên học liệu tương tác và tự sửa khi máy báo sai.
-STEM: Chuỗi thức ăn trong tự nhiên (Khoa học – Mĩ thuật) — dạy thay cho tiết này.
-KNS: KN chăm sóc sức khoẻ bản thân và phòng tránh bệnh tật.</t>
+          <t>Năng lực số 5.2 CB2b: HS dựng đúng chuỗi thức ăn trên học liệu tương tác và tự sửa khi máy báo sai.</t>
         </is>
       </c>
     </row>
@@ -2500,7 +2507,7 @@
       <c r="D66" s="4" t="inlineStr"/>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>Bài 29. Chuỗi thức ăn trong tự nhiên (Tiết 2)</t>
+          <t>Bài 30. Vai trò của thực vật trong chuỗi thức ăn (Tiết 3)</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr"/>
@@ -2511,7 +2518,7 @@
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 2.5 CB2a: HS trình chiếu sơ đồ của nhóm và góp ý cho nhóm bạn một cách lịch sự, đúng mực.</t>
+          <t>Năng lực số 5.2 CB2b: HS dựng đúng chuỗi thức ăn trên học liệu tương tác và tự sửa khi máy báo sai.</t>
         </is>
       </c>
     </row>
@@ -2530,20 +2537,20 @@
       <c r="D67" s="4" t="inlineStr"/>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Bài 29. Chuỗi thức ăn trong tự nhiên (Tiết 3)</t>
-        </is>
-      </c>
-      <c r="F67" s="4" t="inlineStr"/>
+          <t>Bài 31. Ôn tập chủ đề Sinh vật và môi trường</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="H67" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB2b: HS dựng đúng chuỗi thức ăn trên học liệu tương tác và tự sửa khi máy báo sai.</t>
-        </is>
-      </c>
+      <c r="H67" s="4" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
@@ -2553,19 +2560,19 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: Sinh vật và môi trường</t>
+          <t>Ôn tập, kiểm tra, đánh giá</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr"/>
       <c r="D68" s="4" t="inlineStr"/>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>Bài 30. Vai trò của thực vật trong chuỗi thức ăn (Tiết 1)</t>
+          <t>Ôn tập cuối năm (Tiết 1)</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>3 tiết</t>
+          <t>1 tiết</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
@@ -2573,12 +2580,7 @@
           <t>65</t>
         </is>
       </c>
-      <c r="H68" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB2b: HS dựng đúng chuỗi thức ăn trên học liệu tương tác và tự sửa khi máy báo sai.
-KNS: KN chăm sóc sức khoẻ bản thân và phòng tránh bệnh tật.</t>
-        </is>
-      </c>
+      <c r="H68" s="4" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
@@ -2588,27 +2590,27 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: Sinh vật và môi trường</t>
+          <t>Ôn tập, kiểm tra, đánh giá</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr"/>
       <c r="D69" s="4" t="inlineStr"/>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>Bài 30. Vai trò của thực vật trong chuỗi thức ăn (Tiết 2)</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr"/>
+          <t>Ôn tập cuối năm (Tiết 2)</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="H69" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB2b: HS dựng đúng chuỗi thức ăn trên học liệu tương tác và tự sửa khi máy báo sai.</t>
-        </is>
-      </c>
+      <c r="H69" s="4" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
@@ -2618,27 +2620,27 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: Sinh vật và môi trường</t>
+          <t>Ôn tập, kiểm tra, đánh giá</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr"/>
       <c r="D70" s="4" t="inlineStr"/>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>Bài 30. Vai trò của thực vật trong chuỗi thức ăn (Tiết 3)</t>
-        </is>
-      </c>
-      <c r="F70" s="4" t="inlineStr"/>
+          <t>Ôn tập cuối năm (Tiết 3)</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="H70" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB2b: HS dựng đúng chuỗi thức ăn trên học liệu tương tác và tự sửa khi máy báo sai.</t>
-        </is>
-      </c>
+      <c r="H70" s="4" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
@@ -2648,14 +2650,14 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: Sinh vật và môi trường</t>
+          <t>Ôn tập, kiểm tra, đánh giá</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr"/>
       <c r="D71" s="4" t="inlineStr"/>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>Bài 31. Ôn tập chủ đề Sinh vật và môi trường</t>
+          <t>Ôn tập cuối năm (Tiết 4)</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -2685,7 +2687,7 @@
       <c r="D72" s="4" t="inlineStr"/>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>Ôn tập cuối năm học</t>
+          <t>Kiểm tra định kì cuối năm học</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
@@ -2708,14 +2710,14 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Ôn tập, kiểm tra, đánh giá</t>
+          <t>Tiết dự phòng theo SGV</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr"/>
       <c r="D73" s="4" t="inlineStr"/>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>Kiểm tra định kì cuối năm học</t>
+          <t>Tiết dự phòng (nhà trường tự bố trí)</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
@@ -2728,7 +2730,11 @@
           <t>70</t>
         </is>
       </c>
-      <c r="H73" s="4" t="inlineStr"/>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>SGV không xếp bài cho tiết này</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
